--- a/开发文档/温度采样-热敏电阻计算.xlsx
+++ b/开发文档/温度采样-热敏电阻计算.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Intelli_Home\3_Chip_Programming\Circulation_Pump\开发文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BED8FB-0D8C-4D87-8EFA-097011B10268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FCB3ED-0CEE-40E4-9341-12D11871BB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="-110" windowWidth="24420" windowHeight="14620" xr2:uid="{07D0CAF1-0996-41D6-829A-A011ED79B54D}"/>
+    <workbookView xWindow="850" yWindow="-110" windowWidth="24860" windowHeight="14620" activeTab="1" xr2:uid="{07D0CAF1-0996-41D6-829A-A011ED79B54D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="循环泵上热敏电阻" sheetId="2" r:id="rId1"/>
+    <sheet name="卫生间端热敏电阻" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$B$3:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">循环泵上热敏电阻!$B$3:$C$12</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>温度</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,12 +86,28 @@
     <t>电源电压</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>分压电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性值0 处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性值80处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,21 +140,48 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -149,7 +193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -157,6 +201,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -212,7 +274,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$C$3</c:f>
+              <c:f>循环泵上热敏电阻!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -247,7 +309,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$B$4:$B$12</c:f>
+              <c:f>循环泵上热敏电阻!$B$4:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -283,7 +345,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$12</c:f>
+              <c:f>循环泵上热敏电阻!$C$4:$C$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -329,7 +391,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$F$3</c:f>
+              <c:f>循环泵上热敏电阻!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -364,7 +426,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$E$5:$E$12</c:f>
+              <c:f>循环泵上热敏电阻!$E$5:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -397,7 +459,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$F$5:$F$12</c:f>
+              <c:f>循环泵上热敏电阻!$F$5:$F$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -667,39 +729,140 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>循环泵上热敏电阻!$N$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>误差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>循环泵上热敏电阻!$E$4:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>循环泵上热敏电阻!$N$4:$N$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2.5959176637890113</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.40894052590022945</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.32472933586696939</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5.5707843310642602E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5558924729810002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.87621759667322863</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.37805017756901549</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.286686300396056</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.2157347847600306</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9D6A-4579-8EE5-208107BB8723}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="532335695"/>
+        <c:axId val="532337615"/>
+      </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
@@ -708,7 +871,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$3</c:f>
+              <c:f>循环泵上热敏电阻!$O$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -743,32 +906,35 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$E$5:$E$12</c:f>
+              <c:f>循环泵上热敏电阻!$E$4:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>40</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>70</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>80</c:v>
                 </c:pt>
               </c:numCache>
@@ -776,32 +942,35 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$O$5:$O$12</c:f>
+              <c:f>循环泵上热敏电阻!$O$4:$O$12</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>4.0894052590022989E-2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>-1.6236466793348447E-2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>-1.8569281103547608E-3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>1.3897311824524916E-2</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>1.7524351933464466E-2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>6.3008362928169692E-3</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>-1.83812328628008E-2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>-5.2696684809500405E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -822,8 +991,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="532335695"/>
-        <c:axId val="532337615"/>
+        <c:axId val="1335468015"/>
+        <c:axId val="1477861856"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="532335695"/>
@@ -891,7 +1060,8 @@
         <c:axId val="532337615"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="-5.000000000000001E-2"/>
+          <c:max val="5"/>
+          <c:min val="-5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -909,7 +1079,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -950,6 +1120,68 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:valAx>
+        <c:axId val="1477861856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1335468015"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1335468015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1477861856"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -958,6 +1190,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1027,7 +1290,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$E$3</c:f>
+              <c:f>循环泵上热敏电阻!$E$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1063,7 +1326,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$E$4:$E$12</c:f>
+              <c:f>循环泵上热敏电阻!$E$4:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1099,7 +1362,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$E$4:$E$12</c:f>
+              <c:f>循环泵上热敏电阻!$E$4:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1145,7 +1408,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$M$3</c:f>
+              <c:f>循环泵上热敏电阻!$M$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1181,7 +1444,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$E$4:$E$12</c:f>
+              <c:f>循环泵上热敏电阻!$E$4:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1217,7 +1480,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$M$4:$M$12</c:f>
+              <c:f>循环泵上热敏电阻!$M$4:$M$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1501,7 +1764,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$I$3</c:f>
+              <c:f>循环泵上热敏电阻!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1536,7 +1799,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$E$4:$E$12</c:f>
+              <c:f>循环泵上热敏电阻!$E$4:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1572,7 +1835,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$I$4:$I$12</c:f>
+              <c:f>循环泵上热敏电阻!$I$4:$I$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1618,7 +1881,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$J$3</c:f>
+              <c:f>循环泵上热敏电阻!$J$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1653,7 +1916,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$E$4:$E$12</c:f>
+              <c:f>循环泵上热敏电阻!$E$4:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1689,7 +1952,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$J$4:$J$12</c:f>
+              <c:f>循环泵上热敏电阻!$J$4:$J$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1862,6 +2125,1125 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="590069120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>将电压拟合成直线后的误差分析</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>卫生间端热敏电阻!$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>误差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$B$4:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$K$4:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3.0810381956250739</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.54187253348248632</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.27046513672733852</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.30532212885153598</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.13463664397509589</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25290116046417666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-3.7488123002503926E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.3743225933589613</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.1758731193308449</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-8.414565826330545</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C723-42AF-A9C9-7AB435B6BEC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1583099615"/>
+        <c:axId val="1583100575"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>卫生间端热敏电阻!$L$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>误差比例</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$B$4:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$L$4:$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.4187253348248587E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.3523256836366904E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.2212885154061492E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.487888132503226E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.3225290116044608E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.4976246005009628E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.2905376555982682E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-5.9655330276154883E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.10518207282913183</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C723-42AF-A9C9-7AB435B6BEC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1589543071"/>
+        <c:axId val="1589541631"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1583099615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1583100575"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1583100575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3"/>
+          <c:min val="-3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1583099615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1589541631"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.1"/>
+          <c:min val="-0.1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1589543071"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1589543071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1589541631"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>选择分压电阻调整</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>ADC</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>值的线性度</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>卫生间端热敏电阻!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ADC电压</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$B$4:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$F$4:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.46820809248554923</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.70602218700475428</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99887892376681608</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1571428571428573</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3219584569732938</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6530612244897958</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9625550660792952</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2386934673366832</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4681440443213294</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.651785714285714</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4172-4EE1-AB7C-D79566344212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>卫生间端热敏电阻!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>电压线性值</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$B$4:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>卫生间端热敏电阻!$G$4:$G$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.68874999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0074999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1668750000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3262499999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.645</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9637500000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2825000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.6012500000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.92</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4172-4EE1-AB7C-D79566344212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1598147695"/>
+        <c:axId val="1598146255"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1598147695"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1598146255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1598146255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1598147695"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2108,6 +3490,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3661,6 +5123,1038 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4718,6 +7212,83 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="图表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88314409-F12A-6C3F-BFB2-6802F4FADD29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="图表 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74F30026-A8EE-8BF9-17D6-6A808B1BD4E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -5102,7 +7673,7 @@
         <v>0.45</v>
       </c>
       <c r="K4" s="1">
-        <f>(J$12-J$4)/E$12</f>
+        <f t="shared" ref="K4:K12" si="0">(J$12-J$4)/E$12</f>
         <v>2.6875E-2</v>
       </c>
       <c r="L4" s="1">
@@ -5110,7 +7681,7 @@
         <v>0.45</v>
       </c>
       <c r="M4">
-        <f>(I4-L4)/K4</f>
+        <f t="shared" ref="M4:M12" si="1">(I4-L4)/K4</f>
         <v>2.5959176637890113</v>
       </c>
       <c r="N4">
@@ -5142,7 +7713,7 @@
         <v>3.3</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5:I12" si="0">H5/(F5+G5)*G5</f>
+        <f t="shared" ref="I5:I12" si="2">H5/(F5+G5)*G5</f>
         <v>0.72974027663356866</v>
       </c>
       <c r="J5">
@@ -5150,23 +7721,23 @@
         <v>0.71875</v>
       </c>
       <c r="K5" s="1">
-        <f>(J$12-J$4)/E$12</f>
+        <f t="shared" si="0"/>
         <v>2.6875E-2</v>
       </c>
       <c r="L5" s="1">
-        <f t="shared" ref="L5:L12" si="1">J$4</f>
+        <f t="shared" ref="L5:L12" si="3">J$4</f>
         <v>0.45</v>
       </c>
       <c r="M5">
-        <f>(I5-L5)/K5</f>
+        <f t="shared" si="1"/>
         <v>10.408940525900229</v>
       </c>
       <c r="N5">
-        <f t="shared" ref="N5:N12" si="2">M5-E5</f>
+        <f t="shared" ref="N5:N12" si="4">M5-E5</f>
         <v>0.40894052590022945</v>
       </c>
       <c r="O5" s="2">
-        <f t="shared" ref="O5:O12" si="3">M5/E5-1</f>
+        <f t="shared" ref="O5:O12" si="5">M5/E5-1</f>
         <v>4.0894052590022989E-2</v>
       </c>
     </row>
@@ -5190,31 +7761,31 @@
         <v>3.3</v>
       </c>
       <c r="I6">
+        <f t="shared" si="2"/>
+        <v>0.97877289909857512</v>
+      </c>
+      <c r="J6">
+        <f t="shared" ref="J6:J11" si="6">J$4+(J$12-J$4)/8*(ROW()-4)</f>
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="K6" s="1">
         <f t="shared" si="0"/>
-        <v>0.97877289909857512</v>
-      </c>
-      <c r="J6">
-        <f t="shared" ref="J6:J11" si="4">J$4+(J$12-J$4)/8*(ROW()-4)</f>
-        <v>0.98750000000000004</v>
-      </c>
-      <c r="K6" s="1">
-        <f>(J$12-J$4)/E$12</f>
         <v>2.6875E-2</v>
       </c>
       <c r="L6" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="M6">
         <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="M6">
-        <f>(I6-L6)/K6</f>
         <v>19.675270664133031</v>
       </c>
       <c r="N6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.32472933586696939</v>
       </c>
       <c r="O6" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-1.6236466793348447E-2</v>
       </c>
     </row>
@@ -5238,31 +7809,31 @@
         <v>3.3</v>
       </c>
       <c r="I7">
+        <f t="shared" si="2"/>
+        <v>1.2547528517110265</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="6"/>
+        <v>1.2562499999999999</v>
+      </c>
+      <c r="K7" s="1">
         <f t="shared" si="0"/>
-        <v>1.2547528517110265</v>
-      </c>
-      <c r="J7">
+        <v>2.6875E-2</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="1"/>
+        <v>29.944292156689357</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="4"/>
-        <v>1.2562499999999999</v>
-      </c>
-      <c r="K7" s="1">
-        <f>(J$12-J$4)/E$12</f>
-        <v>2.6875E-2</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="M7">
-        <f>(I7-L7)/K7</f>
-        <v>29.944292156689357</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="2"/>
         <v>-5.5707843310642602E-2</v>
       </c>
       <c r="O7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-1.8569281103547608E-3</v>
       </c>
     </row>
@@ -5286,31 +7857,31 @@
         <v>3.3</v>
       </c>
       <c r="I8">
+        <f t="shared" si="2"/>
+        <v>1.5399396102113643</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="6"/>
+        <v>1.5249999999999999</v>
+      </c>
+      <c r="K8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5399396102113643</v>
-      </c>
-      <c r="J8">
+        <v>2.6875E-2</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="1"/>
+        <v>40.555892472981</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="4"/>
-        <v>1.5249999999999999</v>
-      </c>
-      <c r="K8" s="1">
-        <f>(J$12-J$4)/E$12</f>
-        <v>2.6875E-2</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="M8">
-        <f>(I8-L8)/K8</f>
-        <v>40.555892472981</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="2"/>
         <v>0.5558924729810002</v>
       </c>
       <c r="O8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.3897311824524916E-2</v>
       </c>
     </row>
@@ -5334,31 +7905,31 @@
         <v>3.3</v>
       </c>
       <c r="I9">
+        <f t="shared" si="2"/>
+        <v>1.8172983479105929</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="6"/>
+        <v>1.79375</v>
+      </c>
+      <c r="K9" s="1">
         <f t="shared" si="0"/>
-        <v>1.8172983479105929</v>
-      </c>
-      <c r="J9">
+        <v>2.6875E-2</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="1"/>
+        <v>50.876217596673229</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="4"/>
-        <v>1.79375</v>
-      </c>
-      <c r="K9" s="1">
-        <f>(J$12-J$4)/E$12</f>
-        <v>2.6875E-2</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="M9">
-        <f>(I9-L9)/K9</f>
-        <v>50.876217596673229</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="2"/>
         <v>0.87621759667322863</v>
       </c>
       <c r="O9" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7524351933464466E-2</v>
       </c>
     </row>
@@ -5382,31 +7953,31 @@
         <v>3.3</v>
       </c>
       <c r="I10">
+        <f t="shared" si="2"/>
+        <v>2.0726600985221673</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="6"/>
+        <v>2.0625</v>
+      </c>
+      <c r="K10" s="1">
         <f t="shared" si="0"/>
-        <v>2.0726600985221673</v>
-      </c>
-      <c r="J10">
+        <v>2.6875E-2</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="1"/>
+        <v>60.378050177569015</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="4"/>
-        <v>2.0625</v>
-      </c>
-      <c r="K10" s="1">
-        <f>(J$12-J$4)/E$12</f>
-        <v>2.6875E-2</v>
-      </c>
-      <c r="L10" s="1">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="M10">
-        <f>(I10-L10)/K10</f>
-        <v>60.378050177569015</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="2"/>
         <v>0.37805017756901549</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.3008362928169692E-3</v>
       </c>
     </row>
@@ -5430,31 +8001,31 @@
         <v>3.3</v>
       </c>
       <c r="I11">
+        <f t="shared" si="2"/>
+        <v>2.296670305676856</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="6"/>
+        <v>2.3312499999999998</v>
+      </c>
+      <c r="K11" s="1">
         <f t="shared" si="0"/>
-        <v>2.296670305676856</v>
-      </c>
-      <c r="J11">
+        <v>2.6875E-2</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="1"/>
+        <v>68.713313699603944</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="4"/>
-        <v>2.3312499999999998</v>
-      </c>
-      <c r="K11" s="1">
-        <f>(J$12-J$4)/E$12</f>
-        <v>2.6875E-2</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="M11">
-        <f>(I11-L11)/K11</f>
-        <v>68.713313699603944</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="2"/>
         <v>-1.286686300396056</v>
       </c>
       <c r="O11" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-1.83812328628008E-2</v>
       </c>
     </row>
@@ -5478,30 +8049,30 @@
         <v>3.3</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.4867021276595742</v>
       </c>
       <c r="J12">
         <v>2.6</v>
       </c>
       <c r="K12" s="1">
-        <f>(J$12-J$4)/E$12</f>
+        <f t="shared" si="0"/>
         <v>2.6875E-2</v>
       </c>
       <c r="L12" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="M12">
         <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="M12">
-        <f>(I12-L12)/K12</f>
         <v>75.784265215239969</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-4.2157347847600306</v>
       </c>
       <c r="O12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-5.2696684809500405E-2</v>
       </c>
     </row>
@@ -5511,4 +8082,554 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5187725-6207-4688-BD08-75F5336C3996}">
+  <dimension ref="B2:R14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>16.329999999999998</v>
+      </c>
+      <c r="D4">
+        <v>2.7</v>
+      </c>
+      <c r="E4">
+        <v>3.3</v>
+      </c>
+      <c r="F4">
+        <f>E4/(C4+D4)*D4</f>
+        <v>0.46820809248554923</v>
+      </c>
+      <c r="G4">
+        <v>0.37</v>
+      </c>
+      <c r="H4" s="1">
+        <f>(G$13-G$4)/B$13</f>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I4" s="1">
+        <f>G$4</f>
+        <v>0.37</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J12" si="0">(F4-I4)/H4</f>
+        <v>3.0810381956250739</v>
+      </c>
+      <c r="K4">
+        <f>J4-B4</f>
+        <v>3.0810381956250739</v>
+      </c>
+      <c r="L4" s="2" t="e">
+        <f>J4/B4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>2.5</v>
+      </c>
+      <c r="P4">
+        <v>0.32</v>
+      </c>
+      <c r="Q4">
+        <v>2.85</v>
+      </c>
+      <c r="R4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>9.92</v>
+      </c>
+      <c r="D5">
+        <v>2.7</v>
+      </c>
+      <c r="E5">
+        <v>3.3</v>
+      </c>
+      <c r="F5">
+        <f t="shared" ref="F5:F13" si="1">E5/(C5+D5)*D5</f>
+        <v>0.70602218700475428</v>
+      </c>
+      <c r="G5">
+        <f>(G$13-G$4)/(B$13-B$4)*(B5-B$4)+G$4</f>
+        <v>0.68874999999999997</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H13" si="2">(G$13-G$4)/B$13</f>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" ref="I5:I13" si="3">G$4</f>
+        <v>0.37</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:J13" si="4">(F5-I5)/H5</f>
+        <v>10.541872533482486</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ref="K5:K13" si="5">J5-B5</f>
+        <v>0.54187253348248632</v>
+      </c>
+      <c r="L5" s="2">
+        <f t="shared" ref="L5:L13" si="6">J5/B5-1</f>
+        <v>5.4187253348248587E-2</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
+      </c>
+      <c r="P5">
+        <v>0.45</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6">
+        <v>6.22</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>0.99887892376681608</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6:G12" si="7">(G$13-G$4)/(B$13-B$4)*(B6-B$4)+G$4</f>
+        <v>1.0074999999999998</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="4"/>
+        <v>19.729534863272661</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="5"/>
+        <v>-0.27046513672733852</v>
+      </c>
+      <c r="L6" s="8">
+        <f t="shared" si="6"/>
+        <v>-1.3523256836366904E-2</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>3.3</v>
+      </c>
+      <c r="P6">
+        <v>0.51</v>
+      </c>
+      <c r="Q6">
+        <v>3.1</v>
+      </c>
+      <c r="R6">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
+        <v>25</v>
+      </c>
+      <c r="C7" s="6">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="E7" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="1"/>
+        <v>1.1571428571428573</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="7"/>
+        <v>1.1668750000000001</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J7" s="5">
+        <f t="shared" si="4"/>
+        <v>24.694677871148464</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="5"/>
+        <v>-0.30532212885153598</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="6"/>
+        <v>-1.2212885154061492E-2</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>2.7</v>
+      </c>
+      <c r="P7">
+        <v>0.37</v>
+      </c>
+      <c r="Q7">
+        <v>2.92</v>
+      </c>
+      <c r="R7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
+        <v>30</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4.04</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="1"/>
+        <v>1.3219584569732938</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="7"/>
+        <v>1.3262499999999999</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="4"/>
+        <v>29.865363356024904</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="5"/>
+        <v>-0.13463664397509589</v>
+      </c>
+      <c r="L8" s="8">
+        <f t="shared" si="6"/>
+        <v>-4.487888132503226E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
+        <v>40</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2.69</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="1"/>
+        <v>1.6530612244897958</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="7"/>
+        <v>1.645</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="4"/>
+        <v>40.252901160464177</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="5"/>
+        <v>0.25290116046417666</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" si="6"/>
+        <v>6.3225290116044608E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
+        <v>50</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.84</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="1"/>
+        <v>1.9625550660792952</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="7"/>
+        <v>1.9637500000000001</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="4"/>
+        <v>49.962511876997496</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="5"/>
+        <v>-3.7488123002503926E-2</v>
+      </c>
+      <c r="L10" s="8">
+        <f t="shared" si="6"/>
+        <v>-7.4976246005009628E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>60</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1.28</v>
+      </c>
+      <c r="D11">
+        <v>2.7</v>
+      </c>
+      <c r="E11">
+        <v>3.3</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>2.2386934673366832</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="7"/>
+        <v>2.2825000000000002</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="4"/>
+        <v>58.625677406641039</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="5"/>
+        <v>-1.3743225933589613</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="6"/>
+        <v>-2.2905376555982682E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
+        <v>70</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="D12">
+        <v>2.7</v>
+      </c>
+      <c r="E12">
+        <v>3.3</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>2.4681440443213294</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="7"/>
+        <v>2.6012500000000003</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>65.824126880669155</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="5"/>
+        <v>-4.1758731193308449</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="6"/>
+        <v>-5.9655330276154883E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
+        <v>80</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="D13">
+        <v>2.7</v>
+      </c>
+      <c r="E13">
+        <v>3.3</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>2.651785714285714</v>
+      </c>
+      <c r="G13">
+        <v>2.92</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="2"/>
+        <v>3.1875000000000001E-2</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>71.585434173669455</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="5"/>
+        <v>-8.414565826330545</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="6"/>
+        <v>-0.10518207282913183</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>